--- a/public/reports/Final_Report.xlsx
+++ b/public/reports/Final_Report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Job Name</t>
   </si>
@@ -25,10 +25,13 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Office</t>
+  </si>
+  <si>
     <t>Job_1</t>
   </si>
   <si>
-    <t>Alpha_Project</t>
+    <t>Emp1</t>
   </si>
   <si>
     <t>QA</t>
@@ -37,35 +40,14 @@
     <t>Passed</t>
   </si>
   <si>
-    <t>Job_2</t>
-  </si>
-  <si>
-    <t>FAIL_JOB</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>Job_3</t>
-  </si>
-  <si>
-    <t>Charlie_Project</t>
-  </si>
-  <si>
-    <t>Job_4</t>
-  </si>
-  <si>
-    <t>Job_5</t>
-  </si>
-  <si>
-    <t>Echo_Project</t>
+    <t>NY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -76,13 +58,22 @@
     <font>
       <b/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF155724"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -97,9 +88,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -439,13 +431,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="25" customWidth="1"/>
+    <col min="1" max="5" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -458,75 +450,25 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E2" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/public/reports/Final_Report.xlsx
+++ b/public/reports/Final_Report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Job Name</t>
   </si>
@@ -22,25 +22,37 @@
     <t>Environment</t>
   </si>
   <si>
+    <t>Office</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Office</t>
+    <t>Extracted Project Number</t>
+  </si>
+  <si>
+    <t>Extracted Page Job Name</t>
   </si>
   <si>
     <t>Job_1</t>
   </si>
   <si>
-    <t>Emp1</t>
-  </si>
-  <si>
-    <t>QA</t>
+    <t>Alice_Custom</t>
+  </si>
+  <si>
+    <t>https://opensource-demo.orangehrmlive.com/web/index.php/auth/login</t>
+  </si>
+  <si>
+    <t>Smith</t>
   </si>
   <si>
     <t>Passed</t>
   </si>
   <si>
-    <t>NY</t>
+    <t>PRJ-1361</t>
+  </si>
+  <si>
+    <t>OrangeHRM</t>
   </si>
 </sst>
 </file>
@@ -431,13 +443,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="5" width="25" customWidth="1"/>
+    <col min="1" max="7" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,22 +465,34 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
         <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/public/reports/Final_Report.xlsx
+++ b/public/reports/Final_Report.xlsx
@@ -49,7 +49,7 @@
     <t>Passed</t>
   </si>
   <si>
-    <t>PRJ-1361</t>
+    <t>PRJ-9522</t>
   </si>
   <si>
     <t>OrangeHRM</t>
